--- a/templates/default_template.xlsx
+++ b/templates/default_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\파이썬 프로젝트\근무표생성기\근무표서식\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1EDF0AF-E632-43C8-8BB7-333D4E40B8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EBA0AC-8A74-44E8-BC3D-763A76E908BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{6B319A6F-7DAB-44A4-9F23-ACB8B781E5AD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="29">
   <si>
     <t>요일</t>
   </si>
@@ -104,38 +104,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>근무자1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>근무자2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>근무자3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>근무자4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>근무자5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>근무자6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>근무자7</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>근무자8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>일자</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -153,6 +121,30 @@
   </si>
   <si>
     <t>비번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>훈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>연</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>교</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -289,20 +281,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="21">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -594,36 +577,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -635,31 +621,28 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -668,54 +651,42 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="5" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="5" borderId="6" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="5" borderId="7" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1136,239 +1107,185 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441D4944-0881-4D95-B141-076F73D5A323}">
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AL39"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="7.59765625" customWidth="1"/>
-    <col min="2" max="36" width="4.09765625" customWidth="1"/>
-    <col min="37" max="37" width="8.296875" customWidth="1"/>
-    <col min="38" max="38" width="8.796875" customWidth="1"/>
+    <col min="2" max="37" width="4.09765625" customWidth="1"/>
+    <col min="38" max="38" width="8.296875" customWidth="1"/>
+    <col min="39" max="39" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="17.399999999999999" customHeight="1">
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="18" t="s">
+    <row r="1" spans="1:38" ht="17.399999999999999" customHeight="1">
+      <c r="A1" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="35"/>
-      <c r="AG1" s="35"/>
-      <c r="AH1" s="35"/>
-      <c r="AI1" s="35"/>
-      <c r="AJ1" s="35"/>
-      <c r="AK1" s="35"/>
-      <c r="AL1" s="35"/>
-      <c r="AM1" s="35"/>
-      <c r="AN1" s="35"/>
-      <c r="AO1" s="35"/>
-      <c r="AP1" s="35"/>
-      <c r="AQ1" s="35"/>
-      <c r="AR1" s="35"/>
-      <c r="AS1" s="35"/>
-      <c r="AT1" s="35"/>
-      <c r="AU1" s="35"/>
-      <c r="AV1" s="35"/>
-      <c r="AW1" s="35"/>
-      <c r="AX1" s="35"/>
-      <c r="AY1" s="35"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
     </row>
-    <row r="2" spans="1:51" ht="29.55" customHeight="1" thickBot="1">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="35"/>
-      <c r="AO2" s="35"/>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="35"/>
-      <c r="AR2" s="35"/>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="35"/>
-      <c r="AU2" s="35"/>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="35"/>
-      <c r="AY2" s="35"/>
+    <row r="2" spans="1:38" ht="29.55" customHeight="1" thickBot="1">
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="33"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="33"/>
+      <c r="AB2" s="33"/>
+      <c r="AC2" s="33"/>
+      <c r="AD2" s="33"/>
+      <c r="AE2" s="33"/>
+      <c r="AF2" s="33"/>
     </row>
-    <row r="3" spans="1:51" ht="34.049999999999997" customHeight="1" thickBot="1">
-      <c r="A3" s="22" t="s">
+    <row r="3" spans="1:38" ht="34.049999999999997" customHeight="1" thickBot="1">
+      <c r="A3" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="22">
+        <v>1</v>
+      </c>
+      <c r="C3" s="22">
+        <v>2</v>
+      </c>
+      <c r="D3" s="22">
+        <v>3</v>
+      </c>
+      <c r="E3" s="22">
+        <v>4</v>
+      </c>
+      <c r="F3" s="22">
+        <v>5</v>
+      </c>
+      <c r="G3" s="22">
+        <v>6</v>
+      </c>
+      <c r="H3" s="22">
+        <v>7</v>
+      </c>
+      <c r="I3" s="22">
+        <v>8</v>
+      </c>
+      <c r="J3" s="22">
+        <v>9</v>
+      </c>
+      <c r="K3" s="22">
+        <v>10</v>
+      </c>
+      <c r="L3" s="22">
+        <v>11</v>
+      </c>
+      <c r="M3" s="22">
+        <v>12</v>
+      </c>
+      <c r="N3" s="22">
+        <v>13</v>
+      </c>
+      <c r="O3" s="22">
+        <v>14</v>
+      </c>
+      <c r="P3" s="22">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="22">
+        <v>16</v>
+      </c>
+      <c r="R3" s="22">
+        <v>17</v>
+      </c>
+      <c r="S3" s="22">
+        <v>18</v>
+      </c>
+      <c r="T3" s="22">
+        <v>19</v>
+      </c>
+      <c r="U3" s="22">
+        <v>20</v>
+      </c>
+      <c r="V3" s="22">
+        <v>21</v>
+      </c>
+      <c r="W3" s="22">
+        <v>22</v>
+      </c>
+      <c r="X3" s="22">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="22">
+        <v>24</v>
+      </c>
+      <c r="Z3" s="22">
+        <v>25</v>
+      </c>
+      <c r="AA3" s="22">
         <v>26</v>
       </c>
-      <c r="B3" s="23">
-        <v>1</v>
-      </c>
-      <c r="C3" s="23">
-        <v>2</v>
-      </c>
-      <c r="D3" s="23">
-        <v>3</v>
-      </c>
-      <c r="E3" s="23">
-        <v>4</v>
-      </c>
-      <c r="F3" s="23">
-        <v>5</v>
-      </c>
-      <c r="G3" s="23">
-        <v>6</v>
-      </c>
-      <c r="H3" s="23">
-        <v>7</v>
-      </c>
-      <c r="I3" s="23">
-        <v>8</v>
-      </c>
-      <c r="J3" s="23">
-        <v>9</v>
-      </c>
-      <c r="K3" s="23">
-        <v>10</v>
-      </c>
-      <c r="L3" s="23">
-        <v>11</v>
-      </c>
-      <c r="M3" s="23">
-        <v>12</v>
-      </c>
-      <c r="N3" s="23">
-        <v>13</v>
-      </c>
-      <c r="O3" s="23">
-        <v>14</v>
-      </c>
-      <c r="P3" s="23">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="23">
-        <v>16</v>
-      </c>
-      <c r="R3" s="23">
-        <v>17</v>
-      </c>
-      <c r="S3" s="23">
-        <v>18</v>
-      </c>
-      <c r="T3" s="23">
-        <v>19</v>
-      </c>
-      <c r="U3" s="23">
-        <v>20</v>
-      </c>
-      <c r="V3" s="23">
-        <v>21</v>
-      </c>
-      <c r="W3" s="23">
-        <v>22</v>
-      </c>
-      <c r="X3" s="23">
-        <v>23</v>
-      </c>
-      <c r="Y3" s="23">
-        <v>24</v>
-      </c>
-      <c r="Z3" s="23">
-        <v>25</v>
-      </c>
-      <c r="AA3" s="23">
-        <v>26</v>
-      </c>
-      <c r="AB3" s="23">
+      <c r="AB3" s="22">
         <v>27</v>
       </c>
-      <c r="AC3" s="23">
+      <c r="AC3" s="22">
         <v>28</v>
       </c>
-      <c r="AD3" s="23">
+      <c r="AD3" s="22">
         <v>29</v>
       </c>
-      <c r="AE3" s="24">
+      <c r="AE3" s="22">
         <v>30</v>
       </c>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="35"/>
-      <c r="AI3" s="35"/>
-      <c r="AJ3" s="35"/>
-      <c r="AK3" s="35"/>
-      <c r="AL3" s="35"/>
-      <c r="AM3" s="35"/>
-      <c r="AN3" s="35"/>
-      <c r="AO3" s="35"/>
-      <c r="AP3" s="35"/>
-      <c r="AQ3" s="35"/>
-      <c r="AR3" s="35"/>
-      <c r="AS3" s="35"/>
-      <c r="AT3" s="35"/>
-      <c r="AU3" s="35"/>
-      <c r="AV3" s="35"/>
-      <c r="AW3" s="35"/>
-      <c r="AX3" s="35"/>
-      <c r="AY3" s="35"/>
+      <c r="AF3" s="23">
+        <v>31</v>
+      </c>
     </row>
-    <row r="4" spans="1:51" ht="24" customHeight="1">
-      <c r="A4" s="25" t="s">
+    <row r="4" spans="1:38" ht="24" customHeight="1">
+      <c r="A4" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1458,45 +1375,34 @@
       <c r="AD4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AE4" s="26" t="s">
+      <c r="AE4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AF4" s="19" t="s">
+      <c r="AF4" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="AG4" s="7" t="s">
+      <c r="AH4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="AH4" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="AI4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AJ4" s="7" t="s">
+      <c r="AK4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="AK4" s="8" t="s">
+      <c r="AL4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="AL4" s="35"/>
-      <c r="AM4" s="35"/>
-      <c r="AN4" s="35"/>
-      <c r="AO4" s="35"/>
-      <c r="AP4" s="35"/>
-      <c r="AQ4" s="35"/>
-      <c r="AR4" s="35"/>
-      <c r="AS4" s="35"/>
-      <c r="AT4" s="35"/>
-      <c r="AU4" s="35"/>
-      <c r="AV4" s="35"/>
-      <c r="AW4" s="35"/>
-      <c r="AX4" s="35"/>
-      <c r="AY4" s="35"/>
     </row>
-    <row r="5" spans="1:51" ht="30" customHeight="1">
-      <c r="A5" s="27" t="s">
-        <v>18</v>
+    <row r="5" spans="1:38" ht="30" customHeight="1">
+      <c r="A5" s="26" t="s">
+        <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>9</v>
@@ -1579,57 +1485,46 @@
       <c r="AB5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AC5" s="3" t="s">
-        <v>9</v>
+      <c r="AC5" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE5" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF5" s="20">
-        <f t="shared" ref="AF5:AF12" si="0">COUNTIF(B5:AE5,"주")+COUNTIF(B5:AE5,"교")</f>
-        <v>8</v>
-      </c>
-      <c r="AG5" s="17">
-        <f>COUNTIF(B5:AE5,"야")</f>
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF5" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG5" s="19">
+        <f t="shared" ref="AG5:AG24" si="0">COUNTIF(B5:AF5,"주")+COUNTIF(B5:AF5,"교")</f>
+        <v>8</v>
       </c>
       <c r="AH5" s="17">
-        <f>COUNTIF(C5:AF5,"비")</f>
+        <f t="shared" ref="AH5:AH24" si="1">COUNTIF(B5:AF5,"야")</f>
         <v>7</v>
       </c>
       <c r="AI5" s="17">
-        <f>COUNTIF(B5:AE5,"휴")</f>
+        <f>COUNTIF(C5:AG5,"비")</f>
         <v>8</v>
       </c>
       <c r="AJ5" s="17">
-        <f>COUNTIF(B5:AE5,"연")</f>
+        <f t="shared" ref="AJ5:AJ24" si="2">COUNTIF(B5:AF5,"휴")</f>
+        <v>8</v>
+      </c>
+      <c r="AK5" s="17">
+        <f t="shared" ref="AK5:AK24" si="3">COUNTIF(B5:AF5,"연")</f>
         <v>0</v>
       </c>
-      <c r="AK5" s="10">
-        <f>(AF5+AG5+AH5+AJ5)*8</f>
-        <v>176</v>
-      </c>
-      <c r="AL5" s="35"/>
-      <c r="AM5" s="35"/>
-      <c r="AN5" s="35"/>
-      <c r="AO5" s="35"/>
-      <c r="AP5" s="35"/>
-      <c r="AQ5" s="35"/>
-      <c r="AR5" s="35"/>
-      <c r="AS5" s="35"/>
-      <c r="AT5" s="35"/>
-      <c r="AU5" s="35"/>
-      <c r="AV5" s="35"/>
-      <c r="AW5" s="35"/>
-      <c r="AX5" s="35"/>
-      <c r="AY5" s="35"/>
+      <c r="AL5" s="10">
+        <f>(AG5+AH5+AI5+AK5)*8</f>
+        <v>184</v>
+      </c>
     </row>
-    <row r="6" spans="1:51" ht="30" customHeight="1">
-      <c r="A6" s="27" t="s">
-        <v>19</v>
+    <row r="6" spans="1:38" ht="30" customHeight="1">
+      <c r="A6" s="26" t="s">
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
@@ -1712,57 +1607,46 @@
       <c r="AB6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AC6" s="3" t="s">
+      <c r="AC6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="AD6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF6" s="20">
+      <c r="AE6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF6" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG6" s="19">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="AG6" s="17">
-        <f>COUNTIF(B6:AE6,"야")</f>
-        <v>7</v>
-      </c>
       <c r="AH6" s="17">
-        <f t="shared" ref="AH6:AH12" si="1">COUNTIF(C6:AF6,"비")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="AI6" s="17">
-        <f>COUNTIF(B6:AE6,"휴")</f>
+        <f t="shared" ref="AI6:AI24" si="4">COUNTIF(C6:AG6,"비")</f>
         <v>8</v>
       </c>
       <c r="AJ6" s="17">
-        <f>COUNTIF(B6:AE6,"연")</f>
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="AK6" s="17">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AK6" s="10">
-        <f t="shared" ref="AK6:AK12" si="2">(AF6+AG6+AH6+AJ6)*8</f>
-        <v>176</v>
-      </c>
-      <c r="AL6" s="35"/>
-      <c r="AM6" s="35"/>
-      <c r="AN6" s="35"/>
-      <c r="AO6" s="35"/>
-      <c r="AP6" s="35"/>
-      <c r="AQ6" s="35"/>
-      <c r="AR6" s="35"/>
-      <c r="AS6" s="35"/>
-      <c r="AT6" s="35"/>
-      <c r="AU6" s="35"/>
-      <c r="AV6" s="35"/>
-      <c r="AW6" s="35"/>
-      <c r="AX6" s="35"/>
-      <c r="AY6" s="35"/>
+      <c r="AL6" s="10">
+        <f t="shared" ref="AL6:AL24" si="5">(AG6+AH6+AI6+AK6)*8</f>
+        <v>184</v>
+      </c>
     </row>
-    <row r="7" spans="1:51" ht="30" customHeight="1">
-      <c r="A7" s="27" t="s">
-        <v>20</v>
+    <row r="7" spans="1:38" ht="30" customHeight="1">
+      <c r="A7" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>6</v>
@@ -1845,57 +1729,46 @@
       <c r="AB7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AC7" s="3" t="s">
+      <c r="AC7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AD7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="AE7" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF7" s="20">
+      <c r="AE7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF7" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG7" s="19">
         <f t="shared" si="0"/>
         <v>6</v>
-      </c>
-      <c r="AG7" s="17">
-        <f>COUNTIF(B7:AE7,"야")</f>
-        <v>8</v>
       </c>
       <c r="AH7" s="17">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI7" s="17">
-        <f>COUNTIF(B7:AE7,"휴")</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="AJ7" s="17">
-        <f>COUNTIF(B7:AE7,"연")</f>
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="AK7" s="17">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AK7" s="10">
-        <f t="shared" si="2"/>
-        <v>176</v>
-      </c>
-      <c r="AL7" s="35"/>
-      <c r="AM7" s="35"/>
-      <c r="AN7" s="35"/>
-      <c r="AO7" s="35"/>
-      <c r="AP7" s="35"/>
-      <c r="AQ7" s="35"/>
-      <c r="AR7" s="35"/>
-      <c r="AS7" s="35"/>
-      <c r="AT7" s="35"/>
-      <c r="AU7" s="35"/>
-      <c r="AV7" s="35"/>
-      <c r="AW7" s="35"/>
-      <c r="AX7" s="35"/>
-      <c r="AY7" s="35"/>
+      <c r="AL7" s="10">
+        <f t="shared" si="5"/>
+        <v>184</v>
+      </c>
     </row>
-    <row r="8" spans="1:51" ht="30" customHeight="1">
-      <c r="A8" s="27" t="s">
-        <v>21</v>
+    <row r="8" spans="1:38" ht="30" customHeight="1">
+      <c r="A8" s="26" t="s">
+        <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
@@ -1978,57 +1851,46 @@
       <c r="AB8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>9</v>
+      <c r="AC8" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE8" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF8" s="20">
+        <v>9</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF8" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG8" s="19">
         <f t="shared" si="0"/>
         <v>6</v>
-      </c>
-      <c r="AG8" s="17">
-        <f>COUNTIF(B8:AE8,"야")</f>
-        <v>8</v>
       </c>
       <c r="AH8" s="17">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="AI8" s="17">
-        <f>COUNTIF(B8:AE8,"휴")</f>
-        <v>8</v>
+        <f t="shared" si="4"/>
+        <v>9</v>
       </c>
       <c r="AJ8" s="17">
-        <f>COUNTIF(B8:AE8,"연")</f>
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="AK8" s="17">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AK8" s="10">
-        <f t="shared" si="2"/>
-        <v>176</v>
-      </c>
-      <c r="AL8" s="35"/>
-      <c r="AM8" s="35"/>
-      <c r="AN8" s="35"/>
-      <c r="AO8" s="35"/>
-      <c r="AP8" s="35"/>
-      <c r="AQ8" s="35"/>
-      <c r="AR8" s="35"/>
-      <c r="AS8" s="35"/>
-      <c r="AT8" s="35"/>
-      <c r="AU8" s="35"/>
-      <c r="AV8" s="35"/>
-      <c r="AW8" s="35"/>
-      <c r="AX8" s="35"/>
-      <c r="AY8" s="35"/>
+      <c r="AL8" s="10">
+        <f t="shared" si="5"/>
+        <v>184</v>
+      </c>
     </row>
-    <row r="9" spans="1:51" ht="30" customHeight="1">
-      <c r="A9" s="27" t="s">
-        <v>22</v>
+    <row r="9" spans="1:38" ht="30" customHeight="1">
+      <c r="A9" s="26" t="s">
+        <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -2111,57 +1973,46 @@
       <c r="AB9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>8</v>
+      <c r="AC9" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE9" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF9" s="20">
+        <v>8</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF9" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG9" s="19">
         <f t="shared" si="0"/>
         <v>8</v>
-      </c>
-      <c r="AG9" s="17">
-        <f>COUNTIF(B9:AE9,"야")</f>
-        <v>7</v>
       </c>
       <c r="AH9" s="17">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI9" s="17">
-        <f>COUNTIF(B9:AE9,"휴")</f>
-        <v>9</v>
+        <f t="shared" si="4"/>
+        <v>6</v>
       </c>
       <c r="AJ9" s="17">
-        <f>COUNTIF(B9:AE9,"연")</f>
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="AK9" s="17">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AK9" s="10">
-        <f t="shared" si="2"/>
-        <v>168</v>
-      </c>
-      <c r="AL9" s="35"/>
-      <c r="AM9" s="35"/>
-      <c r="AN9" s="35"/>
-      <c r="AO9" s="35"/>
-      <c r="AP9" s="35"/>
-      <c r="AQ9" s="35"/>
-      <c r="AR9" s="35"/>
-      <c r="AS9" s="35"/>
-      <c r="AT9" s="35"/>
-      <c r="AU9" s="35"/>
-      <c r="AV9" s="35"/>
-      <c r="AW9" s="35"/>
-      <c r="AX9" s="35"/>
-      <c r="AY9" s="35"/>
+      <c r="AL9" s="10">
+        <f t="shared" si="5"/>
+        <v>176</v>
+      </c>
     </row>
-    <row r="10" spans="1:51" ht="30" customHeight="1">
-      <c r="A10" s="27" t="s">
-        <v>23</v>
+    <row r="10" spans="1:38" ht="30" customHeight="1">
+      <c r="A10" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>9</v>
@@ -2244,1013 +2095,2308 @@
       <c r="AB10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AC10" s="3" t="s">
+      <c r="AC10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE10" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF10" s="20">
+        <v>7</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG10" s="19">
         <f t="shared" si="0"/>
         <v>8</v>
-      </c>
-      <c r="AG10" s="17">
-        <f>COUNTIF(B10:AE10,"야")</f>
-        <v>7</v>
       </c>
       <c r="AH10" s="17">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI10" s="17">
-        <f>COUNTIF(B10:AE10,"휴")</f>
-        <v>8</v>
+        <f t="shared" si="4"/>
+        <v>7</v>
       </c>
       <c r="AJ10" s="17">
-        <f>COUNTIF(B10:AE10,"연")</f>
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="AK10" s="17">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AK10" s="10">
+      <c r="AL10" s="10">
+        <f t="shared" si="5"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" ht="30" customHeight="1">
+      <c r="A11" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF11" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG11" s="19">
+        <f t="shared" ref="AG11:AG22" si="6">COUNTIF(B11:AF11,"주")+COUNTIF(B11:AF11,"교")</f>
+        <v>6</v>
+      </c>
+      <c r="AH11" s="17">
+        <f t="shared" ref="AH11:AH22" si="7">COUNTIF(B11:AF11,"야")</f>
+        <v>8</v>
+      </c>
+      <c r="AI11" s="17">
+        <f t="shared" ref="AI11:AI22" si="8">COUNTIF(C11:AG11,"비")</f>
+        <v>9</v>
+      </c>
+      <c r="AJ11" s="17">
+        <f t="shared" ref="AJ11:AJ22" si="9">COUNTIF(B11:AF11,"휴")</f>
+        <v>8</v>
+      </c>
+      <c r="AK11" s="17">
+        <f t="shared" ref="AK11:AK22" si="10">COUNTIF(B11:AF11,"연")</f>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="10">
+        <f t="shared" ref="AL11:AL22" si="11">(AG11+AH11+AI11+AK11)*8</f>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" ht="30" customHeight="1">
+      <c r="A12" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF12" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG12" s="19">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="AH12" s="17">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AI12" s="17">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="AJ12" s="17">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="AK12" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL12" s="10">
+        <f t="shared" si="11"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" ht="30" customHeight="1">
+      <c r="A13" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF13" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG13" s="19">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="AH13" s="17">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AI13" s="17">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="AJ13" s="17">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="AK13" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL13" s="10">
+        <f t="shared" si="11"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" ht="30" customHeight="1">
+      <c r="A14" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF14" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="19">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="AH14" s="17">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AI14" s="17">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="AJ14" s="17">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="AK14" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL14" s="10">
+        <f t="shared" si="11"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" ht="30" customHeight="1">
+      <c r="A15" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF15" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG15" s="19">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="AH15" s="17">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AI15" s="17">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="AJ15" s="17">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="AK15" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL15" s="10">
+        <f t="shared" si="11"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" ht="30" customHeight="1">
+      <c r="A16" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF16" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG16" s="19">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="AH16" s="17">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AI16" s="17">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="AJ16" s="17">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="AK16" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL16" s="10">
+        <f t="shared" si="11"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" ht="30" customHeight="1">
+      <c r="A17" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF17" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG17" s="19">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="AH17" s="17">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AI17" s="17">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="AJ17" s="17">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="AK17" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL17" s="10">
+        <f t="shared" si="11"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" ht="30" customHeight="1">
+      <c r="A18" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF18" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG18" s="19">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="AH18" s="17">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AI18" s="17">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="AJ18" s="17">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="AK18" s="17">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AL18" s="10">
+        <f t="shared" si="11"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" ht="30" customHeight="1">
+      <c r="A19" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF19" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG19" s="19">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="AH19" s="17">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AI19" s="17">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="AJ19" s="17">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="AK19" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL19" s="10">
+        <f t="shared" si="11"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" ht="30" customHeight="1">
+      <c r="A20" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF20" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG20" s="19">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="AH20" s="17">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AI20" s="17">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="AJ20" s="17">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="AK20" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL20" s="10">
+        <f t="shared" si="11"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" ht="30" customHeight="1">
+      <c r="A21" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF21" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG21" s="19">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="AH21" s="17">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AI21" s="17">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="AJ21" s="17">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="AK21" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL21" s="10">
+        <f t="shared" si="11"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" ht="30" customHeight="1">
+      <c r="A22" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF22" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG22" s="19">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="AH22" s="17">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AI22" s="17">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="AJ22" s="17">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="AK22" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL22" s="10">
+        <f t="shared" si="11"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" ht="30" customHeight="1">
+      <c r="A23" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF23" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG23" s="19">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AH23" s="17">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="AI23" s="17">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AJ23" s="17">
         <f t="shared" si="2"/>
-        <v>176</v>
-      </c>
-      <c r="AL10" s="35"/>
-      <c r="AM10" s="35"/>
-      <c r="AN10" s="35"/>
-      <c r="AO10" s="35"/>
-      <c r="AP10" s="35"/>
-      <c r="AQ10" s="35"/>
-      <c r="AR10" s="35"/>
-      <c r="AS10" s="35"/>
-      <c r="AT10" s="35"/>
-      <c r="AU10" s="35"/>
-      <c r="AV10" s="35"/>
-      <c r="AW10" s="35"/>
-      <c r="AX10" s="35"/>
-      <c r="AY10" s="35"/>
+        <v>8</v>
+      </c>
+      <c r="AK23" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL23" s="10">
+        <f t="shared" si="5"/>
+        <v>184</v>
+      </c>
     </row>
-    <row r="11" spans="1:51" ht="30" customHeight="1">
-      <c r="A11" s="27" t="s">
+    <row r="24" spans="1:38" ht="30" customHeight="1" thickBot="1">
+      <c r="A24" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE11" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF11" s="20">
+      <c r="B24" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="L24" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="N24" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="O24" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q24" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="R24" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="T24" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="U24" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="V24" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="W24" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="X24" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y24" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z24" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA24" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB24" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC24" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD24" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE24" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG24" s="20">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="AG11" s="17">
-        <f>COUNTIF(B11:AE11,"야")</f>
-        <v>8</v>
-      </c>
-      <c r="AH11" s="17">
+      <c r="AH24" s="9">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="AI11" s="17">
-        <f>COUNTIF(B11:AE11,"휴")</f>
-        <v>9</v>
-      </c>
-      <c r="AJ11" s="17">
-        <f>COUNTIF(B11:AE11,"연")</f>
+        <v>10</v>
+      </c>
+      <c r="AI24" s="17">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="AJ24" s="9">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="AK24" s="9">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AK11" s="10">
-        <f t="shared" si="2"/>
-        <v>168</v>
-      </c>
-      <c r="AL11" s="35"/>
-      <c r="AM11" s="35"/>
-      <c r="AN11" s="35"/>
-      <c r="AO11" s="35"/>
-      <c r="AP11" s="35"/>
-      <c r="AQ11" s="35"/>
-      <c r="AR11" s="35"/>
-      <c r="AS11" s="35"/>
-      <c r="AT11" s="35"/>
-      <c r="AU11" s="35"/>
-      <c r="AV11" s="35"/>
-      <c r="AW11" s="35"/>
-      <c r="AX11" s="35"/>
-      <c r="AY11" s="35"/>
+      <c r="AL24" s="10">
+        <f t="shared" si="5"/>
+        <v>184</v>
+      </c>
     </row>
-    <row r="12" spans="1:51" ht="30" customHeight="1" thickBot="1">
-      <c r="A12" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="L12" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="N12" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="O12" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="P12" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q12" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="R12" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="S12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T12" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="U12" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="V12" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="W12" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="X12" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z12" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA12" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB12" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC12" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD12" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE12" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF12" s="21">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AG12" s="9">
-        <f>COUNTIF(B12:AE12,"야")</f>
-        <v>8</v>
-      </c>
-      <c r="AH12" s="17">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="AI12" s="9">
-        <f>COUNTIF(B12:AE12,"휴")</f>
-        <v>8</v>
-      </c>
-      <c r="AJ12" s="9">
-        <f>COUNTIF(B12:AE12,"연")</f>
+    <row r="25" spans="1:38" ht="31.2" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="12">
+        <f t="shared" ref="B25:AF25" si="12">COUNTIF(B5:B24,"주")</f>
+        <v>2</v>
+      </c>
+      <c r="C25" s="12">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="D25" s="12">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="E25" s="12">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="F25" s="12">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="G25" s="12">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="H25" s="12">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="I25" s="12">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="J25" s="12">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="K25" s="12">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="L25" s="12">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="M25" s="12">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="N25" s="12">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="O25" s="12">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="P25" s="12">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="Q25" s="12">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="R25" s="12">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="S25" s="12">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="T25" s="12">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="U25" s="12">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="V25" s="12">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="W25" s="12">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="X25" s="12">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="Y25" s="12">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="Z25" s="12">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="AA25" s="12">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="AB25" s="12">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="AC25" s="12">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="AD25" s="12">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AK12" s="10">
-        <f t="shared" si="2"/>
-        <v>176</v>
-      </c>
-      <c r="AL12" s="35"/>
-      <c r="AM12" s="35"/>
-      <c r="AN12" s="35"/>
-      <c r="AO12" s="35"/>
-      <c r="AP12" s="35"/>
-      <c r="AQ12" s="35"/>
-      <c r="AR12" s="35"/>
-      <c r="AS12" s="35"/>
-      <c r="AT12" s="35"/>
-      <c r="AU12" s="35"/>
-      <c r="AV12" s="35"/>
-      <c r="AW12" s="35"/>
-      <c r="AX12" s="35"/>
-      <c r="AY12" s="35"/>
+      <c r="AE25" s="12">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="AF25" s="13">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="AG25" s="31"/>
+      <c r="AH25" s="31"/>
+      <c r="AI25" s="31"/>
+      <c r="AJ25" s="31"/>
+      <c r="AK25" s="31"/>
+      <c r="AL25" s="31"/>
     </row>
-    <row r="13" spans="1:51" ht="31.2" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="12">
-        <f>COUNTIF(B5:B12,"주")</f>
+    <row r="26" spans="1:38" ht="31.2" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="11">
+        <f t="shared" ref="B26:AF26" si="13">COUNTIF(B5:B24,"야")</f>
         <v>2</v>
       </c>
-      <c r="C13" s="12">
-        <f>COUNTIF(C5:C12,"주")</f>
+      <c r="C26" s="11">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="D26" s="11">
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="D13" s="12">
-        <f>COUNTIF(D5:D12,"주")</f>
+      <c r="E26" s="11">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="F26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="G26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="H26" s="11">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="I26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="J26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="K26" s="11">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="L26" s="11">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="M26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="N26" s="11">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="O26" s="11">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="P26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="Q26" s="11">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="R26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="S26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="T26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="U26" s="11">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="V26" s="11">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="W26" s="11">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="X26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="Y26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="Z26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="AA26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="AB26" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="AC26" s="11">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="AD26" s="11">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="AE26" s="11">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="AF26" s="14">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="AG26" s="32"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="32"/>
+      <c r="AJ26" s="32"/>
+      <c r="AK26" s="32"/>
+      <c r="AL26" s="32"/>
+    </row>
+    <row r="27" spans="1:38" ht="30.6" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="11">
+        <f t="shared" ref="B27:AF27" si="14">COUNTIF(B4:B23,"비")</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="11">
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="E13" s="12">
-        <f>COUNTIF(E5:E12,"주")</f>
+      <c r="D27" s="11">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="E27" s="11">
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="F13" s="12">
-        <f>COUNTIF(F5:F12,"주")</f>
+      <c r="F27" s="11">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="G27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="H27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="I27" s="11">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="J27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="K27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="L27" s="11">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="M27" s="11">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="N27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="O27" s="11">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="P27" s="11">
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="G13" s="12">
-        <f>COUNTIF(G5:G12,"주")</f>
+      <c r="Q27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="R27" s="11">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="S27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="T27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="U27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="V27" s="11">
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="H13" s="12">
-        <f>COUNTIF(H5:H12,"주")</f>
+      <c r="W27" s="11">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="X27" s="11">
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="I13" s="12">
-        <f>COUNTIF(I5:I12,"주")</f>
+      <c r="Y27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="Z27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="AA27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="AB27" s="11">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="AC27" s="11">
+        <f t="shared" si="14"/>
+        <v>7</v>
+      </c>
+      <c r="AD27" s="11">
+        <f t="shared" ref="AD27" si="15">COUNTIF(AD4:AD23,"비")</f>
+        <v>7</v>
+      </c>
+      <c r="AE27" s="11">
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="J13" s="12">
-        <f>COUNTIF(J5:J12,"주")</f>
+      <c r="AF27" s="14">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="AG27" s="32"/>
+      <c r="AH27" s="32"/>
+      <c r="AI27" s="32"/>
+      <c r="AJ27" s="32"/>
+      <c r="AK27" s="32"/>
+      <c r="AL27" s="32"/>
+    </row>
+    <row r="28" spans="1:38" ht="30.6" customHeight="1" thickBot="1">
+      <c r="A28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="15">
+        <f t="shared" ref="B28:AF28" si="16">COUNTIF(B6:B25,"휴")</f>
+        <v>14</v>
+      </c>
+      <c r="C28" s="15">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+      <c r="D28" s="15">
+        <f t="shared" si="16"/>
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="F28" s="15">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="G28" s="15">
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K13" s="12">
-        <f>COUNTIF(K5:K12,"주")</f>
+      <c r="H28" s="15">
+        <f t="shared" si="16"/>
+        <v>7</v>
+      </c>
+      <c r="I28" s="15">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="J28" s="15">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="K28" s="15">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="L28" s="15">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="M28" s="15">
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="L13" s="12">
-        <f>COUNTIF(L5:L12,"주")</f>
+      <c r="N28" s="15">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="O28" s="15">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="P28" s="15">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q28" s="15">
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="M13" s="12">
-        <f>COUNTIF(M5:M12,"주")</f>
+      <c r="R28" s="15">
+        <f t="shared" si="16"/>
+        <v>11</v>
+      </c>
+      <c r="S28" s="15">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="T28" s="15">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="U28" s="15">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="V28" s="15">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="W28" s="15">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="X28" s="15">
+        <f t="shared" si="16"/>
+        <v>11</v>
+      </c>
+      <c r="Y28" s="15">
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="N13" s="12">
-        <f>COUNTIF(N5:N12,"주")</f>
+      <c r="Z28" s="15">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+      <c r="AA28" s="15">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="AB28" s="15">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="AC28" s="15">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="15">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+      <c r="AE28" s="15">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+      <c r="AF28" s="16">
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="O13" s="12">
-        <f>COUNTIF(O5:O12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="P13" s="12">
-        <f>COUNTIF(P5:P12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="Q13" s="12">
-        <f>COUNTIF(Q5:Q12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="R13" s="12">
-        <f>COUNTIF(R5:R12,"주")</f>
-        <v>1</v>
-      </c>
-      <c r="S13" s="12">
-        <f>COUNTIF(S5:S12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="T13" s="12">
-        <f>COUNTIF(T5:T12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="U13" s="12">
-        <f>COUNTIF(U5:U12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="V13" s="12">
-        <f>COUNTIF(V5:V12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="W13" s="12">
-        <f>COUNTIF(W5:W12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="X13" s="12">
-        <f>COUNTIF(X5:X12,"주")</f>
-        <v>1</v>
-      </c>
-      <c r="Y13" s="12">
-        <f>COUNTIF(Y5:Y12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="Z13" s="12">
-        <f>COUNTIF(Z5:Z12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="AA13" s="12">
-        <f>COUNTIF(AA5:AA12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="AB13" s="12">
-        <f>COUNTIF(AB5:AB12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="AC13" s="12">
-        <f>COUNTIF(AC5:AC12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="AD13" s="12">
-        <f>COUNTIF(AD5:AD12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="AE13" s="13">
-        <f>COUNTIF(AE5:AE12,"주")</f>
-        <v>2</v>
-      </c>
-      <c r="AF13" s="36"/>
-      <c r="AG13" s="36"/>
-      <c r="AH13" s="36"/>
-      <c r="AI13" s="36"/>
-      <c r="AJ13" s="36"/>
-      <c r="AK13" s="36"/>
-      <c r="AL13" s="35"/>
-      <c r="AM13" s="35"/>
-      <c r="AN13" s="35"/>
-      <c r="AO13" s="35"/>
-      <c r="AP13" s="35"/>
-      <c r="AQ13" s="35"/>
-      <c r="AR13" s="35"/>
-      <c r="AS13" s="35"/>
-      <c r="AT13" s="35"/>
-      <c r="AU13" s="35"/>
-      <c r="AV13" s="35"/>
-      <c r="AW13" s="35"/>
-      <c r="AX13" s="35"/>
-      <c r="AY13" s="35"/>
+      <c r="AG28" s="32"/>
+      <c r="AH28" s="32"/>
+      <c r="AI28" s="32"/>
+      <c r="AJ28" s="32"/>
+      <c r="AK28" s="32"/>
+      <c r="AL28" s="32"/>
     </row>
-    <row r="14" spans="1:51" ht="31.2" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="11">
-        <f>COUNTIF(B5:B12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="C14" s="11">
-        <f>COUNTIF(C5:C12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="D14" s="11">
-        <f>COUNTIF(D5:D12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="E14" s="11">
-        <f>COUNTIF(E5:E12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="F14" s="11">
-        <f>COUNTIF(F5:F12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="G14" s="11">
-        <f>COUNTIF(G5:G12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="H14" s="11">
-        <f>COUNTIF(H5:H12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="I14" s="11">
-        <f>COUNTIF(I5:I12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="J14" s="11">
-        <f>COUNTIF(J5:J12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="K14" s="11">
-        <f>COUNTIF(K5:K12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="L14" s="11">
-        <f>COUNTIF(L5:L12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="M14" s="11">
-        <f>COUNTIF(M5:M12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="N14" s="11">
-        <f>COUNTIF(N5:N12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="O14" s="11">
-        <f>COUNTIF(O5:O12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="P14" s="11">
-        <f>COUNTIF(P5:P12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="Q14" s="11">
-        <f>COUNTIF(Q5:Q12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="R14" s="11">
-        <f>COUNTIF(R5:R12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="S14" s="11">
-        <f>COUNTIF(S5:S12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="T14" s="11">
-        <f>COUNTIF(T5:T12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="U14" s="11">
-        <f>COUNTIF(U5:U12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="V14" s="11">
-        <f>COUNTIF(V5:V12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="W14" s="11">
-        <f>COUNTIF(W5:W12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="X14" s="11">
-        <f>COUNTIF(X5:X12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="Y14" s="11">
-        <f>COUNTIF(Y5:Y12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="Z14" s="11">
-        <f>COUNTIF(Z5:Z12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="AA14" s="11">
-        <f>COUNTIF(AA5:AA12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="AB14" s="11">
-        <f>COUNTIF(AB5:AB12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="AC14" s="11">
-        <f>COUNTIF(AC5:AC12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="AD14" s="11">
-        <f>COUNTIF(AD5:AD12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="AE14" s="14">
-        <f>COUNTIF(AE5:AE12,"야")</f>
-        <v>2</v>
-      </c>
-      <c r="AF14" s="37"/>
-      <c r="AG14" s="37"/>
-      <c r="AH14" s="37"/>
-      <c r="AI14" s="37"/>
-      <c r="AJ14" s="37"/>
-      <c r="AK14" s="37"/>
-      <c r="AL14" s="35"/>
-      <c r="AM14" s="35"/>
-      <c r="AN14" s="35"/>
-      <c r="AO14" s="35"/>
-      <c r="AP14" s="35"/>
-      <c r="AQ14" s="35"/>
-      <c r="AR14" s="35"/>
-      <c r="AS14" s="35"/>
-      <c r="AT14" s="35"/>
-      <c r="AU14" s="35"/>
-      <c r="AV14" s="35"/>
-      <c r="AW14" s="35"/>
-      <c r="AX14" s="35"/>
-      <c r="AY14" s="35"/>
-    </row>
-    <row r="15" spans="1:51" ht="30.6" customHeight="1">
-      <c r="A15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="11">
-        <f>COUNTIF(B4:B11,"비")</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="11">
-        <f>COUNTIF(C4:C11,"비")</f>
-        <v>1</v>
-      </c>
-      <c r="D15" s="11">
-        <f>COUNTIF(D4:D11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="E15" s="11">
-        <f>COUNTIF(E4:E11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="F15" s="11">
-        <f>COUNTIF(F4:F11,"비")</f>
-        <v>1</v>
-      </c>
-      <c r="G15" s="11">
-        <f>COUNTIF(G4:G11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="H15" s="11">
-        <f>COUNTIF(H4:H11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="I15" s="11">
-        <f>COUNTIF(I4:I11,"비")</f>
-        <v>1</v>
-      </c>
-      <c r="J15" s="11">
-        <f>COUNTIF(J4:J11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="K15" s="11">
-        <f>COUNTIF(K4:K11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="L15" s="11">
-        <f>COUNTIF(L4:L11,"비")</f>
-        <v>1</v>
-      </c>
-      <c r="M15" s="11">
-        <f>COUNTIF(M4:M11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="N15" s="11">
-        <f>COUNTIF(N4:N11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="O15" s="11">
-        <f>COUNTIF(O4:O11,"비")</f>
-        <v>1</v>
-      </c>
-      <c r="P15" s="11">
-        <f>COUNTIF(P4:P11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="Q15" s="11">
-        <f>COUNTIF(Q4:Q11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="R15" s="11">
-        <f>COUNTIF(R4:R11,"비")</f>
-        <v>1</v>
-      </c>
-      <c r="S15" s="11">
-        <f>COUNTIF(S4:S11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="T15" s="11">
-        <f>COUNTIF(T4:T11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="U15" s="11">
-        <f>COUNTIF(U4:U11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="V15" s="11">
-        <f>COUNTIF(V4:V11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="W15" s="11">
-        <f>COUNTIF(W4:W11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="X15" s="11">
-        <f>COUNTIF(X4:X11,"비")</f>
-        <v>1</v>
-      </c>
-      <c r="Y15" s="11">
-        <f>COUNTIF(Y4:Y11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="Z15" s="11">
-        <f>COUNTIF(Z4:Z11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="AA15" s="11">
-        <f>COUNTIF(AA4:AA11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="AB15" s="11">
-        <f>COUNTIF(AB4:AB11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="AC15" s="11">
-        <f>COUNTIF(AC4:AC11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="AD15" s="11">
-        <f>COUNTIF(AD4:AD11,"비")</f>
-        <v>1</v>
-      </c>
-      <c r="AE15" s="14">
-        <f>COUNTIF(AE4:AE11,"비")</f>
-        <v>2</v>
-      </c>
-      <c r="AF15" s="37"/>
-      <c r="AG15" s="37"/>
-      <c r="AH15" s="37"/>
-      <c r="AI15" s="37"/>
-      <c r="AJ15" s="37"/>
-      <c r="AK15" s="37"/>
-      <c r="AL15" s="35"/>
-      <c r="AM15" s="35"/>
-      <c r="AN15" s="35"/>
-      <c r="AO15" s="35"/>
-      <c r="AP15" s="35"/>
-      <c r="AQ15" s="35"/>
-      <c r="AR15" s="35"/>
-      <c r="AS15" s="35"/>
-      <c r="AT15" s="35"/>
-      <c r="AU15" s="35"/>
-      <c r="AV15" s="35"/>
-      <c r="AW15" s="35"/>
-      <c r="AX15" s="35"/>
-      <c r="AY15" s="35"/>
-    </row>
-    <row r="16" spans="1:51" ht="30.6" customHeight="1" thickBot="1">
-      <c r="A16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="15">
-        <f t="shared" ref="B16:AE16" si="3">COUNTIF(B6:B13,"휴")</f>
-        <v>3</v>
-      </c>
-      <c r="C16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="D16" s="15">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="F16" s="15">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="H16" s="15">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="I16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="J16" s="15">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="L16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="M16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="N16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="O16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="P16" s="15">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Q16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="R16" s="15">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="S16" s="15">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="T16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="U16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="V16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="W16" s="15">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="X16" s="15">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="Y16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="Z16" s="15">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AA16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="AB16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="AC16" s="15">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AD16" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="AE16" s="16">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="AF16" s="37"/>
-      <c r="AG16" s="37"/>
-      <c r="AH16" s="37"/>
-      <c r="AI16" s="37"/>
-      <c r="AJ16" s="37"/>
-      <c r="AK16" s="37"/>
-      <c r="AL16" s="35"/>
-      <c r="AM16" s="35"/>
-      <c r="AN16" s="35"/>
-      <c r="AO16" s="35"/>
-      <c r="AP16" s="35"/>
-      <c r="AQ16" s="35"/>
-      <c r="AR16" s="35"/>
-      <c r="AS16" s="35"/>
-      <c r="AT16" s="35"/>
-      <c r="AU16" s="35"/>
-      <c r="AV16" s="35"/>
-      <c r="AW16" s="35"/>
-      <c r="AX16" s="35"/>
-      <c r="AY16" s="35"/>
-    </row>
-    <row r="17" spans="1:47" ht="96.6" customHeight="1">
-      <c r="A17" s="35"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
-      <c r="AA17" s="35"/>
-      <c r="AB17" s="35"/>
-      <c r="AC17" s="35"/>
-      <c r="AD17" s="35"/>
-      <c r="AE17" s="35"/>
-      <c r="AF17" s="35"/>
-      <c r="AG17" s="35"/>
-      <c r="AH17" s="35"/>
-      <c r="AI17" s="35"/>
-      <c r="AJ17" s="35"/>
-      <c r="AK17" s="35"/>
-      <c r="AL17" s="35"/>
-      <c r="AM17" s="35"/>
-      <c r="AN17" s="35"/>
-      <c r="AO17" s="35"/>
-      <c r="AP17" s="35"/>
-      <c r="AQ17" s="35"/>
-      <c r="AR17" s="35"/>
-      <c r="AS17" s="35"/>
-      <c r="AT17" s="35"/>
-      <c r="AU17" s="35"/>
-    </row>
-    <row r="18" spans="1:47" ht="96.6" customHeight="1">
-      <c r="A18" s="35"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="35"/>
-      <c r="AC18" s="35"/>
-      <c r="AD18" s="35"/>
-      <c r="AE18" s="35"/>
-      <c r="AF18" s="35"/>
-      <c r="AG18" s="35"/>
-      <c r="AH18" s="35"/>
-      <c r="AI18" s="35"/>
-      <c r="AJ18" s="35"/>
-      <c r="AK18" s="35"/>
-      <c r="AL18" s="35"/>
-      <c r="AM18" s="35"/>
-      <c r="AN18" s="35"/>
-      <c r="AO18" s="35"/>
-      <c r="AP18" s="35"/>
-      <c r="AQ18" s="35"/>
-      <c r="AR18" s="35"/>
-      <c r="AS18" s="35"/>
-      <c r="AT18" s="35"/>
-      <c r="AU18" s="35"/>
-    </row>
-    <row r="19" spans="1:47" ht="96.6" customHeight="1"/>
-    <row r="20" spans="1:47" ht="96.6" customHeight="1"/>
-    <row r="21" spans="1:47" ht="96.6" customHeight="1"/>
-    <row r="22" spans="1:47" ht="96.6" customHeight="1"/>
-    <row r="23" spans="1:47" ht="96.6" customHeight="1"/>
-    <row r="24" spans="1:47" ht="96.6" customHeight="1"/>
-    <row r="25" spans="1:47" ht="96.6" customHeight="1"/>
-    <row r="26" spans="1:47" ht="96.6" customHeight="1"/>
-    <row r="27" spans="1:47" ht="96.6" customHeight="1"/>
+    <row r="29" spans="1:38" ht="30.6" customHeight="1"/>
+    <row r="30" spans="1:38" ht="30.6" customHeight="1"/>
+    <row r="31" spans="1:38" ht="30.6" customHeight="1"/>
+    <row r="32" spans="1:38" ht="30.6" customHeight="1"/>
+    <row r="33" ht="30.6" customHeight="1"/>
+    <row r="34" ht="30.6" customHeight="1"/>
+    <row r="35" ht="30.6" customHeight="1"/>
+    <row r="36" ht="30.6" customHeight="1"/>
+    <row r="37" ht="30.6" customHeight="1"/>
+    <row r="38" ht="30.6" customHeight="1"/>
+    <row r="39" ht="30.6" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D1:AA2"/>
+    <mergeCell ref="A1:AF2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B4:AE12">
+  <conditionalFormatting sqref="B4:AF24">
     <cfRule type="containsText" dxfId="6" priority="6" stopIfTrue="1" operator="containsText" text="일">
       <formula>NOT(ISERROR(SEARCH(("일"),(B4))))</formula>
     </cfRule>
@@ -3258,7 +4404,7 @@
       <formula>NOT(ISERROR(SEARCH(("토"),(B4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:AE12">
+  <conditionalFormatting sqref="B5:AF24">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"연"</formula>
     </cfRule>
